--- a/_Page/Supplier/Template-Supplier.xlsx
+++ b/_Page/Supplier/Template-Supplier.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GIGABYTE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\Pharmix\_Page\Supplier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35CB882F-F4C5-4406-A6AD-30E85B0DB58D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB27277-5A12-4624-8917-65D6F02CF6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="1770" windowWidth="18900" windowHeight="11055" xr2:uid="{38D6C9F3-9914-47B5-AA72-A475540EC697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38D6C9F3-9914-47B5-AA72-A475540EC697}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="105">
   <si>
     <t>No</t>
   </si>
@@ -226,6 +226,126 @@
   </si>
   <si>
     <t>02328776262</t>
+  </si>
+  <si>
+    <t>PIC</t>
+  </si>
+  <si>
+    <t>NPWP</t>
+  </si>
+  <si>
+    <t>Pic 1</t>
+  </si>
+  <si>
+    <t>Pic 2</t>
+  </si>
+  <si>
+    <t>Pic 3</t>
+  </si>
+  <si>
+    <t>Pic 4</t>
+  </si>
+  <si>
+    <t>Pic 5</t>
+  </si>
+  <si>
+    <t>Pic 6</t>
+  </si>
+  <si>
+    <t>Pic 7</t>
+  </si>
+  <si>
+    <t>Pic 8</t>
+  </si>
+  <si>
+    <t>Pic 9</t>
+  </si>
+  <si>
+    <t>Pic 10</t>
+  </si>
+  <si>
+    <t>Pic 11</t>
+  </si>
+  <si>
+    <t>Pic 12</t>
+  </si>
+  <si>
+    <t>Pic 13</t>
+  </si>
+  <si>
+    <t>Pic 14</t>
+  </si>
+  <si>
+    <t>Pic 15</t>
+  </si>
+  <si>
+    <t>Pic 16</t>
+  </si>
+  <si>
+    <t>Pic 17</t>
+  </si>
+  <si>
+    <t>Pic 18</t>
+  </si>
+  <si>
+    <t>Pic 19</t>
+  </si>
+  <si>
+    <t>npwp-01</t>
+  </si>
+  <si>
+    <t>npwp-03</t>
+  </si>
+  <si>
+    <t>npwp-04</t>
+  </si>
+  <si>
+    <t>npwp-05</t>
+  </si>
+  <si>
+    <t>npwp-06</t>
+  </si>
+  <si>
+    <t>npwp-07</t>
+  </si>
+  <si>
+    <t>npwp-08</t>
+  </si>
+  <si>
+    <t>npwp-09</t>
+  </si>
+  <si>
+    <t>npwp-2</t>
+  </si>
+  <si>
+    <t>npwp-10</t>
+  </si>
+  <si>
+    <t>npwp-11</t>
+  </si>
+  <si>
+    <t>npwp-12</t>
+  </si>
+  <si>
+    <t>npwp-13</t>
+  </si>
+  <si>
+    <t>npwp-14</t>
+  </si>
+  <si>
+    <t>npwp-15</t>
+  </si>
+  <si>
+    <t>npwp-16</t>
+  </si>
+  <si>
+    <t>npwp-17</t>
+  </si>
+  <si>
+    <t>npwp-18</t>
+  </si>
+  <si>
+    <t>npwp-19</t>
   </si>
 </sst>
 </file>
@@ -308,9 +428,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -348,7 +468,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -454,7 +574,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -596,7 +716,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -604,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F174D29-794E-45AA-878F-AFA0A894E7E6}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" customWidth="1"/>
@@ -614,7 +734,7 @@
     <col min="5" max="5" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,8 +750,14 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -647,8 +773,14 @@
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -664,8 +796,14 @@
       <c r="E3" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -681,8 +819,14 @@
       <c r="E4" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -698,8 +842,14 @@
       <c r="E5" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -715,8 +865,14 @@
       <c r="E6" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -732,8 +888,14 @@
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -749,8 +911,14 @@
       <c r="E8" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -766,8 +934,14 @@
       <c r="E9" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -783,8 +957,14 @@
       <c r="E10" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -800,8 +980,14 @@
       <c r="E11" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -817,8 +1003,14 @@
       <c r="E12" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -834,8 +1026,14 @@
       <c r="E13" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -851,8 +1049,14 @@
       <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -868,8 +1072,14 @@
       <c r="E15" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -885,8 +1095,14 @@
       <c r="E16" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -902,8 +1118,14 @@
       <c r="E17" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -919,8 +1141,14 @@
       <c r="E18" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -936,8 +1164,14 @@
       <c r="E19" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -952,6 +1186,12 @@
       </c>
       <c r="E20" s="2" t="s">
         <v>64</v>
+      </c>
+      <c r="F20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
